--- a/src/fmudesign/examples/fmudesign_ex_onebyone.xlsx
+++ b/src/fmudesign/examples/fmudesign_ex_onebyone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LEVJE/dev_komodo/semeio/src/semeio/fmudesign/examples/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LEVJE/project/ert/src/fmudesign/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA5C94-6A92-AA42-B57D-B44BBB46BAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C16D41-E9C5-FF4B-84FD-AF0AAAD100E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,10 +57,58 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>Alternatives:
-- default: means using RMS_SEED 1000-1001-1002-1003-…
-- None: RMS_SEED is not added as parameter in spreadsheet
-- filname for filw with list of seeds (one column)</t>
+          <t xml:space="preserve">Alternatives:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- default: Use RMS_SEED values 1000, 1001, 1002, ...
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- None: RMS_SEED is not added as parameter in spreadsheet.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Name of file with seeds in the first column (.xlsx, .csv or .txt). The path can be absolute or relative (to input file).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
         </r>
       </text>
     </comment>
@@ -96,29 +144,29 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">- None (no sampled background parameters)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">- name of sheet in current workbook containing distributions for background parameters
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>- name of external file with background parameters (suffix .xlsx or .csv) Must be readable as pandas data frame with parameter names as column headers. Path is relative to where fmudesign is run from.</t>
+          <t xml:space="preserve">- None: No sampled background parameters.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- Name of sheet in current workbook containing distributions for background parameters.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>- Name of external file with background parameters (suffix .xlsx or .csv). Must be readable as pandas data frame with parameter names as column headers. The path can be absolute or relative to the location of this file.</t>
         </r>
       </text>
     </comment>
@@ -132,7 +180,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Set RNG seed for "dist" sensitivities
+          <t xml:space="preserve">Set RNG seed for "dist" sensitivities.
 </t>
         </r>
         <r>
@@ -154,18 +202,18 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">- Integer (e.g. 395830)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>- None (leads to non-reproducible analysis)</t>
+          <t xml:space="preserve">- Integer (e.g. 395830).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>- None: Leads to non-reproducible analysis.</t>
         </r>
       </text>
     </comment>
@@ -190,18 +238,18 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">  -  joint  (default): Adding, removing, or reordering parameters may change samples for other parameters.
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">  -  independent : Samples for unchanged parameters and correlation groups stay the same, provided neither distribution seed nor the sample size changes.</t>
+          <t xml:space="preserve">- joint (default): Adding, removing, or reordering parameters may change samples for other parameters.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>- independent: Samples for unchanged parameters and correlation groups stay the same, provided neither distribution_seed nor the sample size changes.</t>
         </r>
       </text>
     </comment>
@@ -246,7 +294,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> monte carlo sensitivity with one or several parameters specified by dist_name(s) and parameters.</t>
+          <t xml:space="preserve"> Monte Carlo sensitivity with one or several parameters specified by dist_name(s) and parameters.</t>
         </r>
       </text>
     </comment>
@@ -261,7 +309,7 @@
             <charset val="1"/>
           </rPr>
           <t>Optional columns in grey text.
-Numreal: number of realisations per sensitivity/scenario.
+numreal: Number of realisations per sensitivity/scenario.
 Overwrites number of realisations from '</t>
         </r>
         <r>
@@ -328,7 +376,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> only seed is varying. Other parameters are set to default, or specified with dist_name = const
+          <t xml:space="preserve"> Only seed is varying. Other parameters are set to default, or specified with dist_name = const.
 </t>
         </r>
         <r>
@@ -350,7 +398,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> one or two alternative cases (with/without repeated seeds). Use with senscase/value
+          <t xml:space="preserve"> One or two alternative cases (with/without repeated seeds). Use with senscase/value.
 </t>
         </r>
         <r>
@@ -372,7 +420,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> parameters sampled from distributions, use with dist_name and dist_param1…
+          <t xml:space="preserve"> Parameters sampled from distributions, use with dist_name and dist_param1…
 </t>
         </r>
         <r>
@@ -394,7 +442,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> single realisation with parameter values set to default values
+          <t xml:space="preserve"> Single realisation with parameter values set to default values.
 Advanced options:
 </t>
         </r>
@@ -417,7 +465,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> parameter values set to default values, except set of background parameters that are varied
+          <t xml:space="preserve"> Parameter values set to default values, except set of background parameters that are varied.
 </t>
         </r>
         <r>
@@ -439,7 +487,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>parameter values read from an external file, typically createed in another software</t>
+          <t>Parameter values read from an external file, typically created in another software.</t>
         </r>
       </text>
     </comment>
@@ -453,7 +501,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>name of first alternative scenario. Will show up in SENSCASE column in design matrix</t>
+          <t>Name of first alternative scenario. Will show up in SENSCASE column in design matrix.</t>
         </r>
       </text>
     </comment>
@@ -467,7 +515,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>parameter value(s) for first alternative scenario</t>
+          <t>Parameter value(s) for first alternative scenario.</t>
         </r>
       </text>
     </comment>
@@ -481,7 +529,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>name of 2nd alternative scenario. Will show up in SENSCASE column in design matrix</t>
+          <t>Name of 2nd alternative scenario. Will show up in SENSCASE column in design matrix.</t>
         </r>
       </text>
     </comment>
@@ -495,7 +543,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t>parameter value(s) for first alternative scenario</t>
+          <t>Parameter value(s) for first alternative scenario.</t>
         </r>
       </text>
     </comment>
@@ -837,7 +885,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve"> part of dist_name is sufficient for distribution name, but the whole name can be provided</t>
+          <t xml:space="preserve"> part of dist_name is sufficient for distribution name, but the whole name can be provided.</t>
         </r>
       </text>
     </comment>
@@ -1080,7 +1128,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1132,6 +1180,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
